--- a/platform_PiN_output/Somalia___SOM/PiN_pop_step1_Somalia___SOM_1008_03AM.xlsx
+++ b/platform_PiN_output/Somalia___SOM/PiN_pop_step1_Somalia___SOM_1008_03AM.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="host" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="affected_population" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="idp" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:N70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,7 +497,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -547,7 +547,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -592,106 +592,146 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SO1103</t>
+          <t>SO1201</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28236</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+        <v>417944</v>
+      </c>
+      <c r="D4" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>324574</v>
+      </c>
+      <c r="F4" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>88924</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4446</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>93370</v>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SO1104</t>
+          <t>SO1202</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29699</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>84289</v>
+      </c>
+      <c r="D5" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>58091</v>
+      </c>
+      <c r="F5" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>23920</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2278</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>26198</v>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SO1201</t>
+          <t>SO1203</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>417944</v>
+        <v>94074</v>
       </c>
       <c r="D6" t="n">
-        <v>77.7</v>
+        <v>62.6</v>
       </c>
       <c r="E6" t="n">
-        <v>324574</v>
+        <v>58848</v>
       </c>
       <c r="F6" t="n">
-        <v>21.3</v>
+        <v>32.2</v>
       </c>
       <c r="G6" t="n">
-        <v>88924</v>
+        <v>30253</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="I6" t="n">
-        <v>4446</v>
+        <v>2487</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2487</v>
       </c>
       <c r="L6" t="n">
-        <v>22.3</v>
+        <v>37.4</v>
       </c>
       <c r="M6" t="n">
-        <v>93370</v>
+        <v>35226</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -702,34 +742,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SO1202</t>
+          <t>SO1301</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>84289</v>
+        <v>192735</v>
       </c>
       <c r="D7" t="n">
-        <v>68.90000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="E7" t="n">
-        <v>58091</v>
+        <v>124986</v>
       </c>
       <c r="F7" t="n">
-        <v>28.4</v>
+        <v>33.3</v>
       </c>
       <c r="G7" t="n">
-        <v>23920</v>
+        <v>64245</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="I7" t="n">
-        <v>2278</v>
+        <v>3504</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -738,10 +778,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>31.1</v>
+        <v>35.2</v>
       </c>
       <c r="M7" t="n">
-        <v>26198</v>
+        <v>67749</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -752,46 +792,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SO1203</t>
+          <t>SO1302</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>94074</v>
+        <v>40196</v>
       </c>
       <c r="D8" t="n">
-        <v>62.6</v>
+        <v>61.2</v>
       </c>
       <c r="E8" t="n">
-        <v>58848</v>
+        <v>24594</v>
       </c>
       <c r="F8" t="n">
-        <v>32.2</v>
+        <v>36.8</v>
       </c>
       <c r="G8" t="n">
-        <v>30253</v>
+        <v>14809</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="I8" t="n">
-        <v>2487</v>
+        <v>529</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="K8" t="n">
-        <v>2487</v>
+        <v>264</v>
       </c>
       <c r="L8" t="n">
-        <v>37.4</v>
+        <v>38.8</v>
       </c>
       <c r="M8" t="n">
-        <v>35226</v>
+        <v>15602</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -802,34 +842,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SO1301</t>
+          <t>SO1303</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>192735</v>
+        <v>40928</v>
       </c>
       <c r="D9" t="n">
-        <v>64.8</v>
+        <v>82.8</v>
       </c>
       <c r="E9" t="n">
-        <v>124986</v>
+        <v>33885</v>
       </c>
       <c r="F9" t="n">
-        <v>33.3</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
-        <v>64245</v>
+        <v>5711</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>3504</v>
+        <v>1333</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -838,60 +878,60 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>35.2</v>
+        <v>17.2</v>
       </c>
       <c r="M9" t="n">
-        <v>67749</v>
+        <v>7043</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SO1302</t>
+          <t>SO1304</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>40196</v>
+        <v>64154</v>
       </c>
       <c r="D10" t="n">
-        <v>61.2</v>
+        <v>70.7</v>
       </c>
       <c r="E10" t="n">
-        <v>24594</v>
+        <v>45384</v>
       </c>
       <c r="F10" t="n">
-        <v>36.8</v>
+        <v>27.1</v>
       </c>
       <c r="G10" t="n">
-        <v>14809</v>
+        <v>17369</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="I10" t="n">
-        <v>529</v>
+        <v>1401</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>38.8</v>
+        <v>29.3</v>
       </c>
       <c r="M10" t="n">
-        <v>15602</v>
+        <v>18770</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -902,84 +942,84 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SO1303</t>
+          <t>SO1401</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40928</v>
+        <v>115318</v>
       </c>
       <c r="D11" t="n">
-        <v>82.8</v>
+        <v>58.3</v>
       </c>
       <c r="E11" t="n">
-        <v>33885</v>
+        <v>67223</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>5711</v>
+        <v>42629</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="I11" t="n">
-        <v>1333</v>
+        <v>4919</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>547</v>
       </c>
       <c r="L11" t="n">
-        <v>17.2</v>
+        <v>41.7</v>
       </c>
       <c r="M11" t="n">
-        <v>7043</v>
+        <v>48095</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SO1304</t>
+          <t>SO1402</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>64154</v>
+        <v>38116</v>
       </c>
       <c r="D12" t="n">
-        <v>70.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>45384</v>
+        <v>32252</v>
       </c>
       <c r="F12" t="n">
-        <v>27.1</v>
+        <v>14.2</v>
       </c>
       <c r="G12" t="n">
-        <v>17369</v>
+        <v>5401</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="I12" t="n">
-        <v>1401</v>
+        <v>463</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -988,60 +1028,60 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>29.3</v>
+        <v>15.4</v>
       </c>
       <c r="M12" t="n">
-        <v>18770</v>
+        <v>5864</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SO1401</t>
+          <t>SO1403</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>115318</v>
+        <v>35438</v>
       </c>
       <c r="D13" t="n">
-        <v>58.3</v>
+        <v>50.8</v>
       </c>
       <c r="E13" t="n">
-        <v>67223</v>
+        <v>18019</v>
       </c>
       <c r="F13" t="n">
-        <v>37</v>
+        <v>43.1</v>
       </c>
       <c r="G13" t="n">
-        <v>42629</v>
+        <v>15256</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>6.1</v>
       </c>
       <c r="I13" t="n">
-        <v>4919</v>
+        <v>2162</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>547</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>41.7</v>
+        <v>49.2</v>
       </c>
       <c r="M13" t="n">
-        <v>48095</v>
+        <v>17419</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1052,96 +1092,96 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SO1402</t>
+          <t>SO1404</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38116</v>
+        <v>42010</v>
       </c>
       <c r="D14" t="n">
-        <v>84.59999999999999</v>
+        <v>27.6</v>
       </c>
       <c r="E14" t="n">
-        <v>32252</v>
+        <v>11608</v>
       </c>
       <c r="F14" t="n">
-        <v>14.2</v>
+        <v>61.2</v>
       </c>
       <c r="G14" t="n">
-        <v>5401</v>
+        <v>25703</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>463</v>
+        <v>3869</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>829</v>
       </c>
       <c r="L14" t="n">
-        <v>15.4</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>5864</v>
+        <v>30402</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SO1403</t>
+          <t>SO1501</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>35438</v>
+        <v>75107</v>
       </c>
       <c r="D15" t="n">
-        <v>50.8</v>
+        <v>64.3</v>
       </c>
       <c r="E15" t="n">
-        <v>18019</v>
+        <v>48283</v>
       </c>
       <c r="F15" t="n">
-        <v>43.1</v>
+        <v>25.7</v>
       </c>
       <c r="G15" t="n">
-        <v>15256</v>
+        <v>19313</v>
       </c>
       <c r="H15" t="n">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
       <c r="I15" t="n">
-        <v>2162</v>
+        <v>5722</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="L15" t="n">
-        <v>49.2</v>
+        <v>35.7</v>
       </c>
       <c r="M15" t="n">
-        <v>17419</v>
+        <v>26824</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1152,96 +1192,96 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SO1404</t>
+          <t>SO1502</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>42010</v>
+        <v>36288</v>
       </c>
       <c r="D16" t="n">
-        <v>27.6</v>
+        <v>82</v>
       </c>
       <c r="E16" t="n">
-        <v>11608</v>
+        <v>29751</v>
       </c>
       <c r="F16" t="n">
-        <v>61.2</v>
+        <v>11.4</v>
       </c>
       <c r="G16" t="n">
-        <v>25703</v>
+        <v>4136</v>
       </c>
       <c r="H16" t="n">
-        <v>9.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="I16" t="n">
-        <v>3869</v>
+        <v>800</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="K16" t="n">
-        <v>829</v>
+        <v>1601</v>
       </c>
       <c r="L16" t="n">
-        <v>72.40000000000001</v>
+        <v>18</v>
       </c>
       <c r="M16" t="n">
-        <v>30402</v>
+        <v>6537</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SO1501</t>
+          <t>SO1503</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>75107</v>
+        <v>70492</v>
       </c>
       <c r="D17" t="n">
-        <v>64.3</v>
+        <v>15.7</v>
       </c>
       <c r="E17" t="n">
-        <v>48283</v>
+        <v>11089</v>
       </c>
       <c r="F17" t="n">
-        <v>25.7</v>
+        <v>70.8</v>
       </c>
       <c r="G17" t="n">
-        <v>19313</v>
+        <v>49899</v>
       </c>
       <c r="H17" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>5722</v>
+        <v>6336</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="K17" t="n">
-        <v>1788</v>
+        <v>3168</v>
       </c>
       <c r="L17" t="n">
-        <v>35.7</v>
+        <v>84.3</v>
       </c>
       <c r="M17" t="n">
-        <v>26824</v>
+        <v>59403</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1252,96 +1292,96 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SO1502</t>
+          <t>SO1601</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>36288</v>
+        <v>317907</v>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>47.5</v>
       </c>
       <c r="E18" t="n">
-        <v>29751</v>
+        <v>151136</v>
       </c>
       <c r="F18" t="n">
-        <v>11.4</v>
+        <v>48.1</v>
       </c>
       <c r="G18" t="n">
-        <v>4136</v>
+        <v>152873</v>
       </c>
       <c r="H18" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="I18" t="n">
-        <v>800</v>
+        <v>8686</v>
       </c>
       <c r="J18" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="K18" t="n">
-        <v>1601</v>
+        <v>5212</v>
       </c>
       <c r="L18" t="n">
-        <v>18</v>
+        <v>52.5</v>
       </c>
       <c r="M18" t="n">
-        <v>6537</v>
+        <v>166771</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SO1503</t>
+          <t>SO1602</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>70492</v>
+        <v>22612</v>
       </c>
       <c r="D19" t="n">
-        <v>15.7</v>
+        <v>65.2</v>
       </c>
       <c r="E19" t="n">
-        <v>11089</v>
+        <v>14741</v>
       </c>
       <c r="F19" t="n">
-        <v>70.8</v>
+        <v>34.2</v>
       </c>
       <c r="G19" t="n">
-        <v>49899</v>
+        <v>7728</v>
       </c>
       <c r="H19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>6336</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3168</v>
+        <v>143</v>
       </c>
       <c r="L19" t="n">
-        <v>84.3</v>
+        <v>34.8</v>
       </c>
       <c r="M19" t="n">
-        <v>59403</v>
+        <v>7871</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1352,46 +1392,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SO1601</t>
+          <t>SO1603</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>317907</v>
+        <v>43076</v>
       </c>
       <c r="D20" t="n">
-        <v>47.5</v>
+        <v>31.2</v>
       </c>
       <c r="E20" t="n">
-        <v>151136</v>
+        <v>13432</v>
       </c>
       <c r="F20" t="n">
-        <v>48.1</v>
+        <v>55.1</v>
       </c>
       <c r="G20" t="n">
-        <v>152873</v>
+        <v>23715</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>8686</v>
+        <v>2594</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6</v>
+        <v>7.7</v>
       </c>
       <c r="K20" t="n">
-        <v>5212</v>
+        <v>3335</v>
       </c>
       <c r="L20" t="n">
-        <v>52.5</v>
+        <v>68.8</v>
       </c>
       <c r="M20" t="n">
-        <v>166771</v>
+        <v>29644</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1402,46 +1442,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SO1602</t>
+          <t>SO1604</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22612</v>
+        <v>27122</v>
       </c>
       <c r="D21" t="n">
-        <v>65.2</v>
+        <v>30.2</v>
       </c>
       <c r="E21" t="n">
-        <v>14741</v>
+        <v>8188</v>
       </c>
       <c r="F21" t="n">
-        <v>34.2</v>
+        <v>64.2</v>
       </c>
       <c r="G21" t="n">
-        <v>7728</v>
+        <v>17399</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="K21" t="n">
-        <v>143</v>
+        <v>512</v>
       </c>
       <c r="L21" t="n">
-        <v>34.8</v>
+        <v>69.8</v>
       </c>
       <c r="M21" t="n">
-        <v>7871</v>
+        <v>18934</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1452,46 +1492,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SO1603</t>
+          <t>SO1606</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>43076</v>
+        <v>69200</v>
       </c>
       <c r="D22" t="n">
-        <v>31.2</v>
+        <v>54.2</v>
       </c>
       <c r="E22" t="n">
-        <v>13432</v>
+        <v>37496</v>
       </c>
       <c r="F22" t="n">
-        <v>55.1</v>
+        <v>40.5</v>
       </c>
       <c r="G22" t="n">
-        <v>23715</v>
+        <v>28046</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="I22" t="n">
-        <v>2594</v>
+        <v>2439</v>
       </c>
       <c r="J22" t="n">
-        <v>7.7</v>
+        <v>1.8</v>
       </c>
       <c r="K22" t="n">
-        <v>3335</v>
+        <v>1219</v>
       </c>
       <c r="L22" t="n">
-        <v>68.8</v>
+        <v>45.8</v>
       </c>
       <c r="M22" t="n">
-        <v>29644</v>
+        <v>31704</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1502,46 +1542,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SO1604</t>
+          <t>SO1701</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27122</v>
+        <v>128056</v>
       </c>
       <c r="D23" t="n">
-        <v>30.2</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
-        <v>8188</v>
+        <v>58854</v>
       </c>
       <c r="F23" t="n">
-        <v>64.2</v>
+        <v>53.5</v>
       </c>
       <c r="G23" t="n">
-        <v>17399</v>
+        <v>68555</v>
       </c>
       <c r="H23" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="I23" t="n">
-        <v>1023</v>
+        <v>647</v>
       </c>
       <c r="J23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>69.8</v>
+        <v>54</v>
       </c>
       <c r="M23" t="n">
-        <v>18934</v>
+        <v>69202</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1552,76 +1592,96 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SO1605</t>
+          <t>SO1702</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>29034</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+        <v>56167</v>
+      </c>
+      <c r="D24" t="n">
+        <v>13</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7281</v>
+      </c>
+      <c r="F24" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>46806</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1040</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1040</v>
+      </c>
+      <c r="L24" t="n">
+        <v>87</v>
+      </c>
+      <c r="M24" t="n">
+        <v>48886</v>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SO1606</t>
+          <t>SO1703</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>69200</v>
+        <v>76638</v>
       </c>
       <c r="D25" t="n">
-        <v>54.2</v>
+        <v>74.7</v>
       </c>
       <c r="E25" t="n">
-        <v>37496</v>
+        <v>57285</v>
       </c>
       <c r="F25" t="n">
-        <v>40.5</v>
+        <v>18.7</v>
       </c>
       <c r="G25" t="n">
-        <v>28046</v>
+        <v>14321</v>
       </c>
       <c r="H25" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="I25" t="n">
-        <v>2439</v>
+        <v>3484</v>
       </c>
       <c r="J25" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>1219</v>
+        <v>1548</v>
       </c>
       <c r="L25" t="n">
-        <v>45.8</v>
+        <v>25.3</v>
       </c>
       <c r="M25" t="n">
-        <v>31704</v>
+        <v>19353</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1632,46 +1692,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SO1701</t>
+          <t>SO1801</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>128056</v>
+        <v>326014</v>
       </c>
       <c r="D26" t="n">
-        <v>46</v>
+        <v>61.7</v>
       </c>
       <c r="E26" t="n">
-        <v>58854</v>
+        <v>201309</v>
       </c>
       <c r="F26" t="n">
-        <v>53.5</v>
+        <v>27.3</v>
       </c>
       <c r="G26" t="n">
-        <v>68555</v>
+        <v>89075</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="I26" t="n">
-        <v>647</v>
+        <v>17815</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>17815</v>
       </c>
       <c r="L26" t="n">
-        <v>54</v>
+        <v>38.3</v>
       </c>
       <c r="M26" t="n">
-        <v>69202</v>
+        <v>124705</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1682,46 +1742,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SO1702</t>
+          <t>SO1802</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>56167</v>
+        <v>79290</v>
       </c>
       <c r="D27" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="E27" t="n">
-        <v>7281</v>
+        <v>49923</v>
       </c>
       <c r="F27" t="n">
-        <v>83.3</v>
+        <v>28.7</v>
       </c>
       <c r="G27" t="n">
-        <v>46806</v>
+        <v>22759</v>
       </c>
       <c r="H27" t="n">
-        <v>1.9</v>
+        <v>7.7</v>
       </c>
       <c r="I27" t="n">
-        <v>1040</v>
+        <v>6118</v>
       </c>
       <c r="J27" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="K27" t="n">
-        <v>1040</v>
+        <v>489</v>
       </c>
       <c r="L27" t="n">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="M27" t="n">
-        <v>48886</v>
+        <v>29367</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -1732,46 +1792,46 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SO1703</t>
+          <t>SO1803</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>76638</v>
+        <v>86213</v>
       </c>
       <c r="D28" t="n">
-        <v>74.7</v>
+        <v>57.7</v>
       </c>
       <c r="E28" t="n">
-        <v>57285</v>
+        <v>49738</v>
       </c>
       <c r="F28" t="n">
-        <v>18.7</v>
+        <v>40.7</v>
       </c>
       <c r="G28" t="n">
-        <v>14321</v>
+        <v>35054</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="I28" t="n">
-        <v>3484</v>
+        <v>947</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K28" t="n">
-        <v>1548</v>
+        <v>474</v>
       </c>
       <c r="L28" t="n">
-        <v>25.3</v>
+        <v>42.3</v>
       </c>
       <c r="M28" t="n">
-        <v>19353</v>
+        <v>36475</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -1782,46 +1842,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SO1801</t>
+          <t>SO1804</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>326014</v>
+        <v>88844</v>
       </c>
       <c r="D29" t="n">
-        <v>61.7</v>
+        <v>21.3</v>
       </c>
       <c r="E29" t="n">
-        <v>201309</v>
+        <v>18915</v>
       </c>
       <c r="F29" t="n">
-        <v>27.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>89075</v>
+        <v>63624</v>
       </c>
       <c r="H29" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="I29" t="n">
-        <v>17815</v>
+        <v>6305</v>
       </c>
       <c r="J29" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>17815</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>38.3</v>
+        <v>78.7</v>
       </c>
       <c r="M29" t="n">
-        <v>124705</v>
+        <v>69929</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -1832,46 +1892,46 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SO1802</t>
+          <t>SO1901</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>79290</v>
+        <v>100738</v>
       </c>
       <c r="D30" t="n">
-        <v>63</v>
+        <v>57.7</v>
       </c>
       <c r="E30" t="n">
-        <v>49923</v>
+        <v>58161</v>
       </c>
       <c r="F30" t="n">
-        <v>28.7</v>
+        <v>38.4</v>
       </c>
       <c r="G30" t="n">
-        <v>22759</v>
+        <v>38681</v>
       </c>
       <c r="H30" t="n">
-        <v>7.7</v>
+        <v>2.5</v>
       </c>
       <c r="I30" t="n">
-        <v>6118</v>
+        <v>2505</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="K30" t="n">
-        <v>489</v>
+        <v>1391</v>
       </c>
       <c r="L30" t="n">
-        <v>37</v>
+        <v>42.3</v>
       </c>
       <c r="M30" t="n">
-        <v>29367</v>
+        <v>42577</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -1882,46 +1942,46 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SO1803</t>
+          <t>SO1902</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>86213</v>
+        <v>79093</v>
       </c>
       <c r="D31" t="n">
-        <v>57.7</v>
+        <v>61.3</v>
       </c>
       <c r="E31" t="n">
-        <v>49738</v>
+        <v>48476</v>
       </c>
       <c r="F31" t="n">
-        <v>40.7</v>
+        <v>34.9</v>
       </c>
       <c r="G31" t="n">
-        <v>35054</v>
+        <v>27640</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="I31" t="n">
-        <v>947</v>
+        <v>1276</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="K31" t="n">
-        <v>474</v>
+        <v>1701</v>
       </c>
       <c r="L31" t="n">
-        <v>42.3</v>
+        <v>38.7</v>
       </c>
       <c r="M31" t="n">
-        <v>36475</v>
+        <v>30617</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -1932,46 +1992,46 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SO1804</t>
+          <t>SO1903</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>88844</v>
+        <v>59428</v>
       </c>
       <c r="D32" t="n">
-        <v>21.3</v>
+        <v>71</v>
       </c>
       <c r="E32" t="n">
-        <v>18915</v>
+        <v>42180</v>
       </c>
       <c r="F32" t="n">
-        <v>71.59999999999999</v>
+        <v>25.6</v>
       </c>
       <c r="G32" t="n">
-        <v>63624</v>
+        <v>15199</v>
       </c>
       <c r="H32" t="n">
-        <v>7.1</v>
+        <v>2.6</v>
       </c>
       <c r="I32" t="n">
-        <v>6305</v>
+        <v>1537</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="L32" t="n">
-        <v>78.7</v>
+        <v>29</v>
       </c>
       <c r="M32" t="n">
-        <v>69929</v>
+        <v>17248</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -1982,76 +2042,96 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SO1805</t>
+          <t>SO2001</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37688</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+        <v>133133</v>
+      </c>
+      <c r="D33" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E33" t="n">
+        <v>40823</v>
+      </c>
+      <c r="F33" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>88265</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2207</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1839</v>
+      </c>
+      <c r="L33" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="M33" t="n">
+        <v>92310</v>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SO1901</t>
+          <t>SO2003</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>100738</v>
+        <v>27360</v>
       </c>
       <c r="D34" t="n">
-        <v>57.7</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>58161</v>
+        <v>819</v>
       </c>
       <c r="F34" t="n">
-        <v>38.4</v>
+        <v>88</v>
       </c>
       <c r="G34" t="n">
-        <v>38681</v>
+        <v>24083</v>
       </c>
       <c r="H34" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="I34" t="n">
-        <v>2505</v>
+        <v>1311</v>
       </c>
       <c r="J34" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="K34" t="n">
-        <v>1391</v>
+        <v>1147</v>
       </c>
       <c r="L34" t="n">
-        <v>42.3</v>
+        <v>97</v>
       </c>
       <c r="M34" t="n">
-        <v>42577</v>
+        <v>26541</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2062,46 +2142,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SO1902</t>
+          <t>SO2101</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>79093</v>
+        <v>172940</v>
       </c>
       <c r="D35" t="n">
-        <v>61.3</v>
+        <v>40.7</v>
       </c>
       <c r="E35" t="n">
-        <v>48476</v>
+        <v>70334</v>
       </c>
       <c r="F35" t="n">
-        <v>34.9</v>
+        <v>41.6</v>
       </c>
       <c r="G35" t="n">
-        <v>27640</v>
+        <v>71989</v>
       </c>
       <c r="H35" t="n">
-        <v>1.6</v>
+        <v>10</v>
       </c>
       <c r="I35" t="n">
-        <v>1276</v>
+        <v>17377</v>
       </c>
       <c r="J35" t="n">
-        <v>2.2</v>
+        <v>7.7</v>
       </c>
       <c r="K35" t="n">
-        <v>1701</v>
+        <v>13239</v>
       </c>
       <c r="L35" t="n">
-        <v>38.7</v>
+        <v>59.3</v>
       </c>
       <c r="M35" t="n">
-        <v>30617</v>
+        <v>102606</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2112,46 +2192,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SO1903</t>
+          <t>SO2201</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>59428</v>
+        <v>6160</v>
       </c>
       <c r="D36" t="n">
-        <v>71</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>42180</v>
+        <v>4460</v>
       </c>
       <c r="F36" t="n">
-        <v>25.6</v>
+        <v>20.4</v>
       </c>
       <c r="G36" t="n">
-        <v>15199</v>
+        <v>1257</v>
       </c>
       <c r="H36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1537</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9</v>
+        <v>7.2</v>
       </c>
       <c r="K36" t="n">
-        <v>512</v>
+        <v>444</v>
       </c>
       <c r="L36" t="n">
-        <v>29</v>
+        <v>27.6</v>
       </c>
       <c r="M36" t="n">
-        <v>17248</v>
+        <v>1700</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2162,110 +2242,146 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SO1904</t>
+          <t>SO2202</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>49995</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+        <v>29929</v>
+      </c>
+      <c r="D37" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="E37" t="n">
+        <v>18976</v>
+      </c>
+      <c r="F37" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>7132</v>
+      </c>
+      <c r="H37" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2802</v>
+      </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+        <v>1019</v>
+      </c>
+      <c r="L37" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="M37" t="n">
+        <v>10953</v>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SO1905</t>
+          <t>SO2203</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>48425</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+        <v>102440</v>
+      </c>
+      <c r="D38" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>40040</v>
+      </c>
+      <c r="F38" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="G38" t="n">
+        <v>55120</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4160</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3120</v>
+      </c>
+      <c r="L38" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="M38" t="n">
+        <v>62400</v>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SO2001</t>
+          <t>SO2204</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>133133</v>
+        <v>46949</v>
       </c>
       <c r="D39" t="n">
-        <v>30.7</v>
+        <v>55.2</v>
       </c>
       <c r="E39" t="n">
-        <v>40823</v>
+        <v>25915</v>
       </c>
       <c r="F39" t="n">
-        <v>66.3</v>
+        <v>36.2</v>
       </c>
       <c r="G39" t="n">
-        <v>88265</v>
+        <v>16996</v>
       </c>
       <c r="H39" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>2207</v>
+        <v>2356</v>
       </c>
       <c r="J39" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="K39" t="n">
-        <v>1839</v>
+        <v>1683</v>
       </c>
       <c r="L39" t="n">
-        <v>69.3</v>
+        <v>44.8</v>
       </c>
       <c r="M39" t="n">
-        <v>92310</v>
+        <v>21034</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -2276,76 +2392,96 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SO2002</t>
+          <t>SO2205</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>44529</v>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+        <v>21140</v>
+      </c>
+      <c r="D40" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="E40" t="n">
+        <v>14283</v>
+      </c>
+      <c r="F40" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="G40" t="n">
+        <v>5359</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I40" t="n">
+        <v>545</v>
+      </c>
+      <c r="J40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K40" t="n">
+        <v>954</v>
+      </c>
+      <c r="L40" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="M40" t="n">
+        <v>6857</v>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SO2003</t>
+          <t>SO2206</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>27360</v>
+        <v>31281</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>47.8</v>
       </c>
       <c r="E41" t="n">
-        <v>819</v>
+        <v>14947</v>
       </c>
       <c r="F41" t="n">
-        <v>88</v>
+        <v>44.4</v>
       </c>
       <c r="G41" t="n">
-        <v>24083</v>
+        <v>13879</v>
       </c>
       <c r="H41" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="I41" t="n">
-        <v>1311</v>
+        <v>1281</v>
       </c>
       <c r="J41" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="K41" t="n">
-        <v>1147</v>
+        <v>1174</v>
       </c>
       <c r="L41" t="n">
-        <v>97</v>
+        <v>52.2</v>
       </c>
       <c r="M41" t="n">
-        <v>26541</v>
+        <v>16334</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -2356,46 +2492,46 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SO2101</t>
+          <t>SO2207</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>172940</v>
+        <v>48858</v>
       </c>
       <c r="D42" t="n">
-        <v>40.7</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>70334</v>
+        <v>32461</v>
       </c>
       <c r="F42" t="n">
-        <v>41.6</v>
+        <v>29.7</v>
       </c>
       <c r="G42" t="n">
-        <v>71989</v>
+        <v>14513</v>
       </c>
       <c r="H42" t="n">
-        <v>10</v>
+        <v>2.3</v>
       </c>
       <c r="I42" t="n">
-        <v>17377</v>
+        <v>1108</v>
       </c>
       <c r="J42" t="n">
-        <v>7.7</v>
+        <v>1.6</v>
       </c>
       <c r="K42" t="n">
-        <v>13239</v>
+        <v>776</v>
       </c>
       <c r="L42" t="n">
-        <v>59.3</v>
+        <v>33.6</v>
       </c>
       <c r="M42" t="n">
-        <v>102606</v>
+        <v>16397</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -2406,136 +2542,196 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SO2102</t>
+          <t>SO2208</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>45464</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+        <v>31931</v>
+      </c>
+      <c r="D43" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="E43" t="n">
+        <v>21640</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7117</v>
+      </c>
+      <c r="H43" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2116</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1058</v>
+      </c>
+      <c r="L43" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="M43" t="n">
+        <v>10291</v>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SO2103</t>
+          <t>SO2209</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>166456</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+        <v>160918</v>
+      </c>
+      <c r="D44" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="E44" t="n">
+        <v>100333</v>
+      </c>
+      <c r="F44" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G44" t="n">
+        <v>41291</v>
+      </c>
+      <c r="H44" t="n">
+        <v>6</v>
+      </c>
+      <c r="I44" t="n">
+        <v>9647</v>
+      </c>
+      <c r="J44" t="n">
+        <v>6</v>
+      </c>
+      <c r="K44" t="n">
+        <v>9647</v>
+      </c>
+      <c r="L44" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="M44" t="n">
+        <v>60585</v>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SO2104</t>
+          <t>SO2210</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>37503</v>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SO2201</t>
+          <t>SO2211</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6160</v>
+        <v>56819</v>
       </c>
       <c r="D46" t="n">
-        <v>72.40000000000001</v>
+        <v>62.4</v>
       </c>
       <c r="E46" t="n">
-        <v>4460</v>
+        <v>35440</v>
       </c>
       <c r="F46" t="n">
-        <v>20.4</v>
+        <v>28.3</v>
       </c>
       <c r="G46" t="n">
-        <v>1257</v>
+        <v>16070</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1435</v>
       </c>
       <c r="J46" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="K46" t="n">
-        <v>444</v>
+        <v>3874</v>
       </c>
       <c r="L46" t="n">
-        <v>27.6</v>
+        <v>37.6</v>
       </c>
       <c r="M46" t="n">
-        <v>1700</v>
+        <v>21379</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -2546,46 +2742,46 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SO2202</t>
+          <t>SO2212</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>29929</v>
+        <v>11326</v>
       </c>
       <c r="D47" t="n">
-        <v>63.4</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>18976</v>
+        <v>8165</v>
       </c>
       <c r="F47" t="n">
-        <v>23.8</v>
+        <v>19.5</v>
       </c>
       <c r="G47" t="n">
-        <v>7132</v>
+        <v>2213</v>
       </c>
       <c r="H47" t="n">
-        <v>9.4</v>
+        <v>4.7</v>
       </c>
       <c r="I47" t="n">
-        <v>2802</v>
+        <v>527</v>
       </c>
       <c r="J47" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K47" t="n">
-        <v>1019</v>
+        <v>421</v>
       </c>
       <c r="L47" t="n">
-        <v>36.6</v>
+        <v>27.9</v>
       </c>
       <c r="M47" t="n">
-        <v>10953</v>
+        <v>3161</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -2596,46 +2792,46 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SO2203</t>
+          <t>SO2213</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>102440</v>
+        <v>55986</v>
       </c>
       <c r="D48" t="n">
-        <v>39.1</v>
+        <v>68.3</v>
       </c>
       <c r="E48" t="n">
-        <v>40040</v>
+        <v>38244</v>
       </c>
       <c r="F48" t="n">
-        <v>53.8</v>
+        <v>24.5</v>
       </c>
       <c r="G48" t="n">
-        <v>55120</v>
+        <v>13721</v>
       </c>
       <c r="H48" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>4160</v>
+        <v>1656</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="K48" t="n">
-        <v>3120</v>
+        <v>2366</v>
       </c>
       <c r="L48" t="n">
-        <v>60.9</v>
+        <v>31.7</v>
       </c>
       <c r="M48" t="n">
-        <v>62400</v>
+        <v>17742</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -2646,46 +2842,46 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SO2204</t>
+          <t>SO2214</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>46949</v>
+        <v>29679</v>
       </c>
       <c r="D49" t="n">
-        <v>55.2</v>
+        <v>62.7</v>
       </c>
       <c r="E49" t="n">
-        <v>25915</v>
+        <v>18616</v>
       </c>
       <c r="F49" t="n">
-        <v>36.2</v>
+        <v>27</v>
       </c>
       <c r="G49" t="n">
-        <v>16996</v>
+        <v>8011</v>
       </c>
       <c r="H49" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="I49" t="n">
-        <v>2356</v>
+        <v>1831</v>
       </c>
       <c r="J49" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="K49" t="n">
-        <v>1683</v>
+        <v>1221</v>
       </c>
       <c r="L49" t="n">
-        <v>44.8</v>
+        <v>37.3</v>
       </c>
       <c r="M49" t="n">
-        <v>21034</v>
+        <v>11063</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -2696,46 +2892,46 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SO2205</t>
+          <t>SO2215</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>21140</v>
+        <v>246091</v>
       </c>
       <c r="D50" t="n">
-        <v>67.59999999999999</v>
+        <v>55.3</v>
       </c>
       <c r="E50" t="n">
-        <v>14283</v>
+        <v>136106</v>
       </c>
       <c r="F50" t="n">
-        <v>25.3</v>
+        <v>38.5</v>
       </c>
       <c r="G50" t="n">
-        <v>5359</v>
+        <v>94862</v>
       </c>
       <c r="H50" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="I50" t="n">
-        <v>545</v>
+        <v>10998</v>
       </c>
       <c r="J50" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="K50" t="n">
-        <v>954</v>
+        <v>4124</v>
       </c>
       <c r="L50" t="n">
-        <v>32.4</v>
+        <v>44.7</v>
       </c>
       <c r="M50" t="n">
-        <v>6857</v>
+        <v>109985</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -2746,46 +2942,46 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SO2206</t>
+          <t>SO2216</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>31281</v>
+        <v>49364</v>
       </c>
       <c r="D51" t="n">
-        <v>47.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>14947</v>
+        <v>33363</v>
       </c>
       <c r="F51" t="n">
-        <v>44.4</v>
+        <v>25.5</v>
       </c>
       <c r="G51" t="n">
-        <v>13879</v>
+        <v>12596</v>
       </c>
       <c r="H51" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1362</v>
+      </c>
+      <c r="J51" t="n">
         <v>4.1</v>
       </c>
-      <c r="I51" t="n">
-        <v>1281</v>
-      </c>
-      <c r="J51" t="n">
-        <v>3.8</v>
-      </c>
       <c r="K51" t="n">
-        <v>1174</v>
+        <v>2043</v>
       </c>
       <c r="L51" t="n">
-        <v>52.2</v>
+        <v>32.4</v>
       </c>
       <c r="M51" t="n">
-        <v>16334</v>
+        <v>16001</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -2796,46 +2992,46 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SO2207</t>
+          <t>SO2217</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>48858</v>
+        <v>37897</v>
       </c>
       <c r="D52" t="n">
-        <v>66.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>32461</v>
+        <v>25231</v>
       </c>
       <c r="F52" t="n">
-        <v>29.7</v>
+        <v>25.9</v>
       </c>
       <c r="G52" t="n">
-        <v>14513</v>
+        <v>9829</v>
       </c>
       <c r="H52" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="I52" t="n">
-        <v>1108</v>
+        <v>912</v>
       </c>
       <c r="J52" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="K52" t="n">
-        <v>776</v>
+        <v>1925</v>
       </c>
       <c r="L52" t="n">
-        <v>33.6</v>
+        <v>33.4</v>
       </c>
       <c r="M52" t="n">
-        <v>16397</v>
+        <v>12666</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -2846,46 +3042,46 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SO2208</t>
+          <t>SO2301</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>31931</v>
+        <v>123497</v>
       </c>
       <c r="D53" t="n">
-        <v>67.8</v>
+        <v>54.2</v>
       </c>
       <c r="E53" t="n">
-        <v>21640</v>
+        <v>66961</v>
       </c>
       <c r="F53" t="n">
-        <v>22.3</v>
+        <v>43.8</v>
       </c>
       <c r="G53" t="n">
-        <v>7117</v>
+        <v>54130</v>
       </c>
       <c r="H53" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="I53" t="n">
-        <v>2116</v>
+        <v>802</v>
       </c>
       <c r="J53" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="K53" t="n">
-        <v>1058</v>
+        <v>1604</v>
       </c>
       <c r="L53" t="n">
-        <v>32.2</v>
+        <v>45.8</v>
       </c>
       <c r="M53" t="n">
-        <v>10291</v>
+        <v>56536</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -2896,46 +3092,46 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SO2209</t>
+          <t>SO2302</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>160918</v>
+        <v>227654</v>
       </c>
       <c r="D54" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E54" t="n">
+        <v>53621</v>
+      </c>
+      <c r="F54" t="n">
         <v>62.4</v>
       </c>
-      <c r="E54" t="n">
-        <v>100333</v>
-      </c>
-      <c r="F54" t="n">
-        <v>25.7</v>
-      </c>
       <c r="G54" t="n">
-        <v>41291</v>
+        <v>142049</v>
       </c>
       <c r="H54" t="n">
-        <v>6</v>
+        <v>10.7</v>
       </c>
       <c r="I54" t="n">
-        <v>9647</v>
+        <v>24459</v>
       </c>
       <c r="J54" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="K54" t="n">
-        <v>9647</v>
+        <v>7526</v>
       </c>
       <c r="L54" t="n">
-        <v>37.6</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M54" t="n">
-        <v>60585</v>
+        <v>174033</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -2946,46 +3142,46 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SO2210</t>
+          <t>SO2303</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C55" t="n">
+        <v>21091</v>
+      </c>
+      <c r="D55" t="n">
+        <v>75</v>
+      </c>
+      <c r="E55" t="n">
+        <v>15818</v>
+      </c>
+      <c r="F55" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5013</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I55" t="n">
+        <v>259</v>
+      </c>
+      <c r="J55" t="n">
         <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>3.5</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>52.2</v>
+        <v>25</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>5273</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -2996,96 +3192,96 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SO2211</t>
+          <t>SO2307</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>56819</v>
+        <v>167182</v>
       </c>
       <c r="D56" t="n">
-        <v>62.4</v>
+        <v>6.4</v>
       </c>
       <c r="E56" t="n">
-        <v>35440</v>
+        <v>10671</v>
       </c>
       <c r="F56" t="n">
-        <v>28.3</v>
+        <v>60.4</v>
       </c>
       <c r="G56" t="n">
-        <v>16070</v>
+        <v>101021</v>
       </c>
       <c r="H56" t="n">
-        <v>2.5</v>
+        <v>27.7</v>
       </c>
       <c r="I56" t="n">
-        <v>1435</v>
+        <v>46242</v>
       </c>
       <c r="J56" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="K56" t="n">
-        <v>3874</v>
+        <v>9248</v>
       </c>
       <c r="L56" t="n">
-        <v>37.6</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>21379</v>
+        <v>156511</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SO2212</t>
+          <t>SO2401</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>11326</v>
+        <v>114149</v>
       </c>
       <c r="D57" t="n">
-        <v>72.09999999999999</v>
+        <v>36.5</v>
       </c>
       <c r="E57" t="n">
-        <v>8165</v>
+        <v>41623</v>
       </c>
       <c r="F57" t="n">
-        <v>19.5</v>
+        <v>52.5</v>
       </c>
       <c r="G57" t="n">
-        <v>2213</v>
+        <v>59912</v>
       </c>
       <c r="H57" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="I57" t="n">
-        <v>527</v>
+        <v>1892</v>
       </c>
       <c r="J57" t="n">
-        <v>3.7</v>
+        <v>9.4</v>
       </c>
       <c r="K57" t="n">
-        <v>421</v>
+        <v>10721</v>
       </c>
       <c r="L57" t="n">
-        <v>27.9</v>
+        <v>63.5</v>
       </c>
       <c r="M57" t="n">
-        <v>3161</v>
+        <v>72526</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -3096,46 +3292,46 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SO2213</t>
+          <t>SO2402</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>55986</v>
+        <v>90174</v>
       </c>
       <c r="D58" t="n">
-        <v>68.3</v>
+        <v>41.4</v>
       </c>
       <c r="E58" t="n">
-        <v>38244</v>
+        <v>37369</v>
       </c>
       <c r="F58" t="n">
-        <v>24.5</v>
+        <v>52.9</v>
       </c>
       <c r="G58" t="n">
-        <v>13721</v>
+        <v>47660</v>
       </c>
       <c r="H58" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="I58" t="n">
-        <v>1656</v>
+        <v>542</v>
       </c>
       <c r="J58" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="K58" t="n">
-        <v>2366</v>
+        <v>4603</v>
       </c>
       <c r="L58" t="n">
-        <v>31.7</v>
+        <v>58.6</v>
       </c>
       <c r="M58" t="n">
-        <v>17742</v>
+        <v>52805</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -3146,46 +3342,46 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SO2214</t>
+          <t>SO2403</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>29679</v>
+        <v>68073</v>
       </c>
       <c r="D59" t="n">
-        <v>62.7</v>
+        <v>43</v>
       </c>
       <c r="E59" t="n">
-        <v>18616</v>
+        <v>29252</v>
       </c>
       <c r="F59" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="G59" t="n">
-        <v>8011</v>
+        <v>37454</v>
       </c>
       <c r="H59" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="I59" t="n">
-        <v>1831</v>
+        <v>820</v>
       </c>
       <c r="J59" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="K59" t="n">
-        <v>1221</v>
+        <v>547</v>
       </c>
       <c r="L59" t="n">
-        <v>37.3</v>
+        <v>57</v>
       </c>
       <c r="M59" t="n">
-        <v>11063</v>
+        <v>38821</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -3196,46 +3392,46 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SO2215</t>
+          <t>SO2404</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>246091</v>
+        <v>40743</v>
       </c>
       <c r="D60" t="n">
-        <v>55.3</v>
+        <v>42.2</v>
       </c>
       <c r="E60" t="n">
-        <v>136106</v>
+        <v>17198</v>
       </c>
       <c r="F60" t="n">
-        <v>38.5</v>
+        <v>54.8</v>
       </c>
       <c r="G60" t="n">
-        <v>94862</v>
+        <v>22317</v>
       </c>
       <c r="H60" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>10998</v>
+        <v>819</v>
       </c>
       <c r="J60" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>4124</v>
+        <v>409</v>
       </c>
       <c r="L60" t="n">
-        <v>44.7</v>
+        <v>57.8</v>
       </c>
       <c r="M60" t="n">
-        <v>109985</v>
+        <v>23545</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -3246,46 +3442,46 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SO2216</t>
+          <t>SO2501</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>49364</v>
+        <v>30087</v>
       </c>
       <c r="D61" t="n">
-        <v>67.59999999999999</v>
+        <v>24.4</v>
       </c>
       <c r="E61" t="n">
-        <v>33363</v>
+        <v>7344</v>
       </c>
       <c r="F61" t="n">
-        <v>25.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>12596</v>
+        <v>21637</v>
       </c>
       <c r="H61" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="I61" t="n">
-        <v>1362</v>
+        <v>790</v>
       </c>
       <c r="J61" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>2043</v>
+        <v>316</v>
       </c>
       <c r="L61" t="n">
-        <v>32.4</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="M61" t="n">
-        <v>16001</v>
+        <v>22743</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -3296,46 +3492,46 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SO2217</t>
+          <t>SO2502</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37897</v>
+        <v>35051</v>
       </c>
       <c r="D62" t="n">
-        <v>66.59999999999999</v>
+        <v>44.2</v>
       </c>
       <c r="E62" t="n">
-        <v>25231</v>
+        <v>15496</v>
       </c>
       <c r="F62" t="n">
-        <v>25.9</v>
+        <v>45.3</v>
       </c>
       <c r="G62" t="n">
-        <v>9829</v>
+        <v>15865</v>
       </c>
       <c r="H62" t="n">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="I62" t="n">
-        <v>912</v>
+        <v>3505</v>
       </c>
       <c r="J62" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="K62" t="n">
-        <v>1925</v>
+        <v>184</v>
       </c>
       <c r="L62" t="n">
-        <v>33.4</v>
+        <v>55.8</v>
       </c>
       <c r="M62" t="n">
-        <v>12666</v>
+        <v>19555</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -3346,46 +3542,46 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SO2301</t>
+          <t>SO2504</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>123497</v>
+        <v>35536</v>
       </c>
       <c r="D63" t="n">
-        <v>54.2</v>
+        <v>38.8</v>
       </c>
       <c r="E63" t="n">
-        <v>66961</v>
+        <v>13779</v>
       </c>
       <c r="F63" t="n">
-        <v>43.8</v>
+        <v>50.6</v>
       </c>
       <c r="G63" t="n">
-        <v>54130</v>
+        <v>17969</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6</v>
+        <v>8.6</v>
       </c>
       <c r="I63" t="n">
-        <v>802</v>
+        <v>3062</v>
       </c>
       <c r="J63" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>1604</v>
+        <v>725</v>
       </c>
       <c r="L63" t="n">
-        <v>45.8</v>
+        <v>61.2</v>
       </c>
       <c r="M63" t="n">
-        <v>56536</v>
+        <v>21757</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -3396,46 +3592,46 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SO2302</t>
+          <t>SO2601</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>227654</v>
+        <v>62595</v>
       </c>
       <c r="D64" t="n">
-        <v>23.6</v>
+        <v>60.2</v>
       </c>
       <c r="E64" t="n">
-        <v>53621</v>
+        <v>37705</v>
       </c>
       <c r="F64" t="n">
-        <v>62.4</v>
+        <v>27.6</v>
       </c>
       <c r="G64" t="n">
-        <v>142049</v>
+        <v>17251</v>
       </c>
       <c r="H64" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="I64" t="n">
-        <v>24459</v>
+        <v>5914</v>
       </c>
       <c r="J64" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="K64" t="n">
-        <v>7526</v>
+        <v>1725</v>
       </c>
       <c r="L64" t="n">
-        <v>76.40000000000001</v>
+        <v>39.8</v>
       </c>
       <c r="M64" t="n">
-        <v>174033</v>
+        <v>24890</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -3446,46 +3642,46 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SO2303</t>
+          <t>SO2602</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>21091</v>
+        <v>56220</v>
       </c>
       <c r="D65" t="n">
-        <v>75</v>
+        <v>54.1</v>
       </c>
       <c r="E65" t="n">
-        <v>15818</v>
+        <v>30395</v>
       </c>
       <c r="F65" t="n">
-        <v>23.8</v>
+        <v>41.1</v>
       </c>
       <c r="G65" t="n">
-        <v>5013</v>
+        <v>23082</v>
       </c>
       <c r="H65" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I65" t="n">
+        <v>2057</v>
+      </c>
+      <c r="J65" t="n">
         <v>1.2</v>
       </c>
-      <c r="I65" t="n">
-        <v>259</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="L65" t="n">
-        <v>25</v>
+        <v>45.9</v>
       </c>
       <c r="M65" t="n">
-        <v>5273</v>
+        <v>25825</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -3496,1096 +3692,250 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SO2304</t>
+          <t>SO2604</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>34117</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+        <v>40699</v>
+      </c>
+      <c r="D66" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="E66" t="n">
+        <v>23366</v>
+      </c>
+      <c r="F66" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="G66" t="n">
+        <v>12370</v>
+      </c>
+      <c r="H66" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I66" t="n">
+        <v>4352</v>
+      </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
+        <v>611</v>
+      </c>
+      <c r="L66" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="M66" t="n">
+        <v>17333</v>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SO2305</t>
+          <t>SO2605</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>66972</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+        <v>36859</v>
+      </c>
+      <c r="D67" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="E67" t="n">
+        <v>17201</v>
+      </c>
+      <c r="F67" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>10734</v>
+      </c>
+      <c r="H67" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="I67" t="n">
+        <v>6337</v>
+      </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+        <v>2587</v>
+      </c>
+      <c r="L67" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="M67" t="n">
+        <v>19658</v>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SO2306</t>
+          <t>SO2606</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>33498</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+        <v>37992</v>
+      </c>
+      <c r="D68" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="E68" t="n">
+        <v>19141</v>
+      </c>
+      <c r="F68" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="G68" t="n">
+        <v>17981</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I68" t="n">
+        <v>870</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="M68" t="n">
+        <v>18851</v>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SO2307</t>
+          <t>SO2801</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>167182</v>
+        <v>79724</v>
       </c>
       <c r="D69" t="n">
-        <v>6.4</v>
+        <v>63.9</v>
       </c>
       <c r="E69" t="n">
-        <v>10671</v>
+        <v>50971</v>
       </c>
       <c r="F69" t="n">
-        <v>60.4</v>
+        <v>32.2</v>
       </c>
       <c r="G69" t="n">
-        <v>101021</v>
+        <v>25703</v>
       </c>
       <c r="H69" t="n">
-        <v>27.7</v>
+        <v>3.3</v>
       </c>
       <c r="I69" t="n">
-        <v>46242</v>
+        <v>2614</v>
       </c>
       <c r="J69" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="K69" t="n">
-        <v>9248</v>
+        <v>436</v>
       </c>
       <c r="L69" t="n">
-        <v>93.59999999999999</v>
+        <v>36.1</v>
       </c>
       <c r="M69" t="n">
-        <v>156511</v>
+        <v>28753</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SO2401</t>
+          <t>SO2802</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>host</t>
+          <t>affected_population</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>114149</v>
+        <v>96867</v>
       </c>
       <c r="D70" t="n">
-        <v>36.5</v>
+        <v>42.6</v>
       </c>
       <c r="E70" t="n">
-        <v>41623</v>
+        <v>41281</v>
       </c>
       <c r="F70" t="n">
-        <v>52.5</v>
+        <v>48.5</v>
       </c>
       <c r="G70" t="n">
-        <v>59912</v>
+        <v>47003</v>
       </c>
       <c r="H70" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="I70" t="n">
-        <v>1892</v>
+        <v>7357</v>
       </c>
       <c r="J70" t="n">
-        <v>9.4</v>
+        <v>1.3</v>
       </c>
       <c r="K70" t="n">
-        <v>10721</v>
+        <v>1226</v>
       </c>
       <c r="L70" t="n">
-        <v>63.5</v>
+        <v>57.4</v>
       </c>
       <c r="M70" t="n">
-        <v>72526</v>
+        <v>55586</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>SO2402</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>90174</v>
-      </c>
-      <c r="D71" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="E71" t="n">
-        <v>37369</v>
-      </c>
-      <c r="F71" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="G71" t="n">
-        <v>47660</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I71" t="n">
-        <v>542</v>
-      </c>
-      <c r="J71" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K71" t="n">
-        <v>4603</v>
-      </c>
-      <c r="L71" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="M71" t="n">
-        <v>52805</v>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>SO2403</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>68073</v>
-      </c>
-      <c r="D72" t="n">
-        <v>43</v>
-      </c>
-      <c r="E72" t="n">
-        <v>29252</v>
-      </c>
-      <c r="F72" t="n">
-        <v>55</v>
-      </c>
-      <c r="G72" t="n">
-        <v>37454</v>
-      </c>
-      <c r="H72" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I72" t="n">
-        <v>820</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K72" t="n">
-        <v>547</v>
-      </c>
-      <c r="L72" t="n">
-        <v>57</v>
-      </c>
-      <c r="M72" t="n">
-        <v>38821</v>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>SO2404</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>40743</v>
-      </c>
-      <c r="D73" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="E73" t="n">
-        <v>17198</v>
-      </c>
-      <c r="F73" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="G73" t="n">
-        <v>22317</v>
-      </c>
-      <c r="H73" t="n">
-        <v>2</v>
-      </c>
-      <c r="I73" t="n">
-        <v>819</v>
-      </c>
-      <c r="J73" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" t="n">
-        <v>409</v>
-      </c>
-      <c r="L73" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="M73" t="n">
-        <v>23545</v>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>SO2501</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>30087</v>
-      </c>
-      <c r="D74" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E74" t="n">
-        <v>7344</v>
-      </c>
-      <c r="F74" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="G74" t="n">
-        <v>21637</v>
-      </c>
-      <c r="H74" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I74" t="n">
-        <v>790</v>
-      </c>
-      <c r="J74" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" t="n">
-        <v>316</v>
-      </c>
-      <c r="L74" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="M74" t="n">
-        <v>22743</v>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>SO2502</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>35051</v>
-      </c>
-      <c r="D75" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="E75" t="n">
-        <v>15496</v>
-      </c>
-      <c r="F75" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="G75" t="n">
-        <v>15865</v>
-      </c>
-      <c r="H75" t="n">
-        <v>10</v>
-      </c>
-      <c r="I75" t="n">
-        <v>3505</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K75" t="n">
-        <v>184</v>
-      </c>
-      <c r="L75" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="M75" t="n">
-        <v>19555</v>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>SO2503</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>73943</v>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>SO2504</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>35536</v>
-      </c>
-      <c r="D77" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="E77" t="n">
-        <v>13779</v>
-      </c>
-      <c r="F77" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="G77" t="n">
-        <v>17969</v>
-      </c>
-      <c r="H77" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I77" t="n">
-        <v>3062</v>
-      </c>
-      <c r="J77" t="n">
-        <v>2</v>
-      </c>
-      <c r="K77" t="n">
-        <v>725</v>
-      </c>
-      <c r="L77" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="M77" t="n">
-        <v>21757</v>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>SO2505</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>40029</v>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>SO2601</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>62595</v>
-      </c>
-      <c r="D79" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="E79" t="n">
-        <v>37705</v>
-      </c>
-      <c r="F79" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="G79" t="n">
-        <v>17251</v>
-      </c>
-      <c r="H79" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I79" t="n">
-        <v>5914</v>
-      </c>
-      <c r="J79" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K79" t="n">
-        <v>1725</v>
-      </c>
-      <c r="L79" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="M79" t="n">
-        <v>24890</v>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>SO2602</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>56220</v>
-      </c>
-      <c r="D80" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="E80" t="n">
-        <v>30395</v>
-      </c>
-      <c r="F80" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="G80" t="n">
-        <v>23082</v>
-      </c>
-      <c r="H80" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I80" t="n">
-        <v>2057</v>
-      </c>
-      <c r="J80" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K80" t="n">
-        <v>686</v>
-      </c>
-      <c r="L80" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="M80" t="n">
-        <v>25825</v>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>SO2603</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>77096</v>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>SO2604</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>40699</v>
-      </c>
-      <c r="D82" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="E82" t="n">
-        <v>23366</v>
-      </c>
-      <c r="F82" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="G82" t="n">
-        <v>12370</v>
-      </c>
-      <c r="H82" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="I82" t="n">
-        <v>4352</v>
-      </c>
-      <c r="J82" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K82" t="n">
-        <v>611</v>
-      </c>
-      <c r="L82" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="M82" t="n">
-        <v>17333</v>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>SO2605</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>36859</v>
-      </c>
-      <c r="D83" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="E83" t="n">
-        <v>17201</v>
-      </c>
-      <c r="F83" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="G83" t="n">
-        <v>10734</v>
-      </c>
-      <c r="H83" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="I83" t="n">
-        <v>6337</v>
-      </c>
-      <c r="J83" t="n">
-        <v>7</v>
-      </c>
-      <c r="K83" t="n">
-        <v>2587</v>
-      </c>
-      <c r="L83" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M83" t="n">
-        <v>19658</v>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>SO2606</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>37992</v>
-      </c>
-      <c r="D84" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="E84" t="n">
-        <v>19141</v>
-      </c>
-      <c r="F84" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="G84" t="n">
-        <v>17981</v>
-      </c>
-      <c r="H84" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I84" t="n">
-        <v>870</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="M84" t="n">
-        <v>18851</v>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>SO2701</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>66770</v>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>SO2702</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>75529</v>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>SO2703</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>50014</v>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>SO2801</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>79724</v>
-      </c>
-      <c r="D88" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="E88" t="n">
-        <v>50971</v>
-      </c>
-      <c r="F88" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="G88" t="n">
-        <v>25703</v>
-      </c>
-      <c r="H88" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I88" t="n">
-        <v>2614</v>
-      </c>
-      <c r="J88" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K88" t="n">
-        <v>436</v>
-      </c>
-      <c r="L88" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="M88" t="n">
-        <v>28753</v>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>SO2802</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>96867</v>
-      </c>
-      <c r="D89" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="E89" t="n">
-        <v>41281</v>
-      </c>
-      <c r="F89" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="G89" t="n">
-        <v>47003</v>
-      </c>
-      <c r="H89" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I89" t="n">
-        <v>7357</v>
-      </c>
-      <c r="J89" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K89" t="n">
-        <v>1226</v>
-      </c>
-      <c r="L89" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="M89" t="n">
-        <v>55586</v>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>SO2803</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>37711</v>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>SO2804</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>196269</v>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -4600,7 +3950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4728,7 +4078,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SO1103</t>
+          <t>SO1201</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4737,28 +4087,48 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3977</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+        <v>50210</v>
+      </c>
+      <c r="D3" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>30925</v>
+      </c>
+      <c r="F3" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>18937</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>174</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>174</v>
+      </c>
+      <c r="L3" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>19285</v>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SO1201</t>
+          <t>SO1303</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4767,37 +4137,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50210</v>
+        <v>2939</v>
       </c>
       <c r="D4" t="n">
-        <v>61.6</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>30925</v>
+        <v>2339</v>
       </c>
       <c r="F4" t="n">
-        <v>37.7</v>
+        <v>17.9</v>
       </c>
       <c r="G4" t="n">
-        <v>18937</v>
+        <v>525</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="I4" t="n">
-        <v>174</v>
+        <v>75</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>38.4</v>
+        <v>20.4</v>
       </c>
       <c r="M4" t="n">
-        <v>19285</v>
+        <v>600</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4808,7 +4178,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SO1303</t>
+          <t>SO1401</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4817,25 +4187,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2939</v>
+        <v>2951</v>
       </c>
       <c r="D5" t="n">
-        <v>79.59999999999999</v>
+        <v>27.5</v>
       </c>
       <c r="E5" t="n">
-        <v>2339</v>
+        <v>813</v>
       </c>
       <c r="F5" t="n">
-        <v>17.9</v>
+        <v>69.8</v>
       </c>
       <c r="G5" t="n">
-        <v>525</v>
+        <v>2059</v>
       </c>
       <c r="H5" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="I5" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -4844,10 +4214,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>20.4</v>
+        <v>72.5</v>
       </c>
       <c r="M5" t="n">
-        <v>600</v>
+        <v>2138</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4858,7 +4228,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SO1401</t>
+          <t>SO1402</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4867,25 +4237,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2951</v>
+        <v>4952</v>
       </c>
       <c r="D6" t="n">
-        <v>27.5</v>
+        <v>95</v>
       </c>
       <c r="E6" t="n">
-        <v>813</v>
+        <v>4706</v>
       </c>
       <c r="F6" t="n">
-        <v>69.8</v>
+        <v>3.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2059</v>
+        <v>172</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="I6" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -4894,21 +4264,21 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>72.5</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>2138</v>
+        <v>246</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SO1402</t>
+          <t>SO1403</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4917,25 +4287,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4952</v>
+        <v>6127</v>
       </c>
       <c r="D7" t="n">
-        <v>95</v>
+        <v>12.3</v>
       </c>
       <c r="E7" t="n">
-        <v>4706</v>
+        <v>755</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5</v>
+        <v>87</v>
       </c>
       <c r="G7" t="n">
-        <v>172</v>
+        <v>5328</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="I7" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -4944,21 +4314,21 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>87.7</v>
       </c>
       <c r="M7" t="n">
-        <v>246</v>
+        <v>5372</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SO1403</t>
+          <t>SO1404</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4967,25 +4337,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6127</v>
+        <v>908</v>
       </c>
       <c r="D8" t="n">
-        <v>12.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="n">
-        <v>755</v>
+        <v>142</v>
       </c>
       <c r="F8" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G8" t="n">
-        <v>5328</v>
+        <v>672</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7</v>
+        <v>10.4</v>
       </c>
       <c r="I8" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -4994,10 +4364,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>87.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>5372</v>
+        <v>766</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -5008,7 +4378,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SO1404</t>
+          <t>SO1501</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5017,37 +4387,37 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>908</v>
+        <v>4309</v>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>35.6</v>
       </c>
       <c r="E9" t="n">
-        <v>142</v>
+        <v>1533</v>
       </c>
       <c r="F9" t="n">
-        <v>74</v>
+        <v>54.8</v>
       </c>
       <c r="G9" t="n">
-        <v>672</v>
+        <v>2362</v>
       </c>
       <c r="H9" t="n">
-        <v>10.4</v>
+        <v>6.7</v>
       </c>
       <c r="I9" t="n">
-        <v>94</v>
+        <v>290</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="L9" t="n">
-        <v>84.40000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>766</v>
+        <v>2776</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -5058,7 +4428,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SO1501</t>
+          <t>SO1502</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5067,37 +4437,37 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4309</v>
+        <v>5338</v>
       </c>
       <c r="D10" t="n">
-        <v>35.6</v>
+        <v>60.9</v>
       </c>
       <c r="E10" t="n">
-        <v>1533</v>
+        <v>3249</v>
       </c>
       <c r="F10" t="n">
-        <v>54.8</v>
+        <v>36.2</v>
       </c>
       <c r="G10" t="n">
-        <v>2362</v>
+        <v>1934</v>
       </c>
       <c r="H10" t="n">
-        <v>6.7</v>
+        <v>2.9</v>
       </c>
       <c r="I10" t="n">
-        <v>290</v>
+        <v>155</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>64.40000000000001</v>
+        <v>39.1</v>
       </c>
       <c r="M10" t="n">
-        <v>2776</v>
+        <v>2089</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -5108,7 +4478,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SO1502</t>
+          <t>SO1503</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5117,48 +4487,48 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5338</v>
+        <v>430</v>
       </c>
       <c r="D11" t="n">
-        <v>60.9</v>
+        <v>2.9</v>
       </c>
       <c r="E11" t="n">
-        <v>3249</v>
+        <v>13</v>
       </c>
       <c r="F11" t="n">
-        <v>36.2</v>
+        <v>75.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1934</v>
+        <v>326</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>155</v>
+        <v>38</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="L11" t="n">
-        <v>39.1</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>2089</v>
+        <v>417</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SO1503</t>
+          <t>SO1601</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5167,48 +4537,48 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>430</v>
+        <v>39813</v>
       </c>
       <c r="D12" t="n">
-        <v>2.9</v>
+        <v>26.1</v>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>10395</v>
       </c>
       <c r="F12" t="n">
-        <v>75.7</v>
+        <v>66.5</v>
       </c>
       <c r="G12" t="n">
-        <v>326</v>
+        <v>26477</v>
       </c>
       <c r="H12" t="n">
-        <v>8.699999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>38</v>
+        <v>1765</v>
       </c>
       <c r="J12" t="n">
-        <v>12.6</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>54</v>
+        <v>1177</v>
       </c>
       <c r="L12" t="n">
-        <v>97.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>417</v>
+        <v>29418</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SO1601</t>
+          <t>SO1606</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5217,37 +4587,37 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>39813</v>
+        <v>6758</v>
       </c>
       <c r="D13" t="n">
-        <v>26.1</v>
+        <v>26.4</v>
       </c>
       <c r="E13" t="n">
-        <v>10395</v>
+        <v>1781</v>
       </c>
       <c r="F13" t="n">
-        <v>66.5</v>
+        <v>56.4</v>
       </c>
       <c r="G13" t="n">
-        <v>26477</v>
+        <v>3813</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>15.2</v>
       </c>
       <c r="I13" t="n">
-        <v>1765</v>
+        <v>1027</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>1177</v>
+        <v>137</v>
       </c>
       <c r="L13" t="n">
-        <v>73.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>29418</v>
+        <v>4977</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -5258,7 +4628,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SO1606</t>
+          <t>SO1701</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5267,37 +4637,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6758</v>
+        <v>21432</v>
       </c>
       <c r="D14" t="n">
-        <v>26.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>1781</v>
+        <v>1768</v>
       </c>
       <c r="F14" t="n">
-        <v>56.4</v>
+        <v>82</v>
       </c>
       <c r="G14" t="n">
-        <v>3813</v>
+        <v>17565</v>
       </c>
       <c r="H14" t="n">
-        <v>15.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>1027</v>
+        <v>2099</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>73.59999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="M14" t="n">
-        <v>4977</v>
+        <v>19664</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -5308,7 +4678,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SO1701</t>
+          <t>SO1801</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5317,37 +4687,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21432</v>
+        <v>45076</v>
       </c>
       <c r="D15" t="n">
-        <v>8.199999999999999</v>
+        <v>33.5</v>
       </c>
       <c r="E15" t="n">
-        <v>1768</v>
+        <v>15100</v>
       </c>
       <c r="F15" t="n">
-        <v>82</v>
+        <v>51.5</v>
       </c>
       <c r="G15" t="n">
-        <v>17565</v>
+        <v>23214</v>
       </c>
       <c r="H15" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>2099</v>
+        <v>3155</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3606</v>
       </c>
       <c r="L15" t="n">
-        <v>91.8</v>
+        <v>66.5</v>
       </c>
       <c r="M15" t="n">
-        <v>19664</v>
+        <v>29976</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -5358,7 +4728,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SO1801</t>
+          <t>SO1802</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5367,37 +4737,37 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>45076</v>
+        <v>3778</v>
       </c>
       <c r="D16" t="n">
-        <v>33.5</v>
+        <v>40.2</v>
       </c>
       <c r="E16" t="n">
-        <v>15100</v>
+        <v>1519</v>
       </c>
       <c r="F16" t="n">
-        <v>51.5</v>
+        <v>58.2</v>
       </c>
       <c r="G16" t="n">
-        <v>23214</v>
+        <v>2201</v>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="I16" t="n">
-        <v>3155</v>
+        <v>58</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3606</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>66.5</v>
+        <v>59.8</v>
       </c>
       <c r="M16" t="n">
-        <v>29976</v>
+        <v>2259</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -5408,7 +4778,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SO1802</t>
+          <t>SO1803</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5417,25 +4787,25 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3778</v>
+        <v>270</v>
       </c>
       <c r="D17" t="n">
-        <v>40.2</v>
+        <v>30.7</v>
       </c>
       <c r="E17" t="n">
-        <v>1519</v>
+        <v>83</v>
       </c>
       <c r="F17" t="n">
-        <v>58.2</v>
+        <v>69.3</v>
       </c>
       <c r="G17" t="n">
-        <v>2201</v>
+        <v>187</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -5444,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>59.8</v>
+        <v>69.3</v>
       </c>
       <c r="M17" t="n">
-        <v>2259</v>
+        <v>187</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -5458,7 +4828,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SO1803</t>
+          <t>SO1901</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5467,37 +4837,37 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>270</v>
+        <v>14588</v>
       </c>
       <c r="D18" t="n">
-        <v>30.7</v>
+        <v>25.6</v>
       </c>
       <c r="E18" t="n">
-        <v>83</v>
+        <v>3741</v>
       </c>
       <c r="F18" t="n">
-        <v>69.3</v>
+        <v>62.8</v>
       </c>
       <c r="G18" t="n">
-        <v>187</v>
+        <v>9164</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1262</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="L18" t="n">
-        <v>69.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>187</v>
+        <v>10847</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -5508,7 +4878,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SO1805</t>
+          <t>SO1903</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5517,36 +4887,48 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+        <v>3188</v>
+      </c>
+      <c r="D19" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1475</v>
+      </c>
+      <c r="F19" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1566</v>
+      </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="L19" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1713</v>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SO1901</t>
+          <t>SO2001</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5555,37 +4937,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14588</v>
+        <v>19871</v>
       </c>
       <c r="D20" t="n">
-        <v>25.6</v>
+        <v>3.3</v>
       </c>
       <c r="E20" t="n">
-        <v>3741</v>
+        <v>656</v>
       </c>
       <c r="F20" t="n">
-        <v>62.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>9164</v>
+        <v>18363</v>
       </c>
       <c r="H20" t="n">
-        <v>8.699999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="I20" t="n">
-        <v>1262</v>
+        <v>525</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="K20" t="n">
-        <v>421</v>
+        <v>328</v>
       </c>
       <c r="L20" t="n">
-        <v>74.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="M20" t="n">
-        <v>10847</v>
+        <v>19215</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -5596,7 +4978,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SO1903</t>
+          <t>SO2003</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5605,48 +4987,48 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3188</v>
+        <v>1436</v>
       </c>
       <c r="D21" t="n">
-        <v>46.3</v>
+        <v>1.7</v>
       </c>
       <c r="E21" t="n">
-        <v>1475</v>
+        <v>24</v>
       </c>
       <c r="F21" t="n">
-        <v>49.1</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>1566</v>
+        <v>1047</v>
       </c>
       <c r="H21" t="n">
         <v>3.4</v>
       </c>
       <c r="I21" t="n">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2</v>
+        <v>22</v>
       </c>
       <c r="K21" t="n">
-        <v>39</v>
+        <v>316</v>
       </c>
       <c r="L21" t="n">
-        <v>53.7</v>
+        <v>98.3</v>
       </c>
       <c r="M21" t="n">
-        <v>1713</v>
+        <v>1412</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SO1904</t>
+          <t>SO2101</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5655,40 +5037,48 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>21609</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>16.1</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+        <v>3480</v>
+      </c>
+      <c r="F22" t="n">
+        <v>67</v>
+      </c>
+      <c r="G22" t="n">
+        <v>14487</v>
+      </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>15.7</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>3399</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+        <v>243</v>
+      </c>
+      <c r="L22" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="M22" t="n">
+        <v>18129</v>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SO2001</t>
+          <t>SO2203</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5697,37 +5087,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>19871</v>
+        <v>218656</v>
       </c>
       <c r="D23" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
       <c r="E23" t="n">
-        <v>656</v>
+        <v>14577</v>
       </c>
       <c r="F23" t="n">
-        <v>92.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="G23" t="n">
-        <v>18363</v>
+        <v>189502</v>
       </c>
       <c r="H23" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="I23" t="n">
-        <v>525</v>
+        <v>11338</v>
       </c>
       <c r="J23" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="K23" t="n">
-        <v>328</v>
+        <v>3239</v>
       </c>
       <c r="L23" t="n">
-        <v>96.7</v>
+        <v>93.3</v>
       </c>
       <c r="M23" t="n">
-        <v>19215</v>
+        <v>204079</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -5738,7 +5128,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SO2002</t>
+          <t>SO2210</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5747,28 +5137,48 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>776</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+        <v>222742</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8428</v>
+      </c>
+      <c r="F24" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>201070</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>13244</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>214314</v>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SO2003</t>
+          <t>SO2301</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5777,48 +5187,48 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1436</v>
+        <v>7265</v>
       </c>
       <c r="D25" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="F25" t="n">
-        <v>72.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>1047</v>
+        <v>6818</v>
       </c>
       <c r="H25" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="I25" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="J25" t="n">
-        <v>22</v>
+        <v>3.3</v>
       </c>
       <c r="K25" t="n">
-        <v>316</v>
+        <v>238</v>
       </c>
       <c r="L25" t="n">
-        <v>98.3</v>
+        <v>98</v>
       </c>
       <c r="M25" t="n">
-        <v>1412</v>
+        <v>7116</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SO2101</t>
+          <t>SO2302</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5827,37 +5237,37 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>21609</v>
+        <v>22260</v>
       </c>
       <c r="D26" t="n">
-        <v>16.1</v>
+        <v>11.2</v>
       </c>
       <c r="E26" t="n">
-        <v>3480</v>
+        <v>2484</v>
       </c>
       <c r="F26" t="n">
-        <v>67</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>14487</v>
+        <v>19500</v>
       </c>
       <c r="H26" t="n">
-        <v>15.7</v>
+        <v>1.2</v>
       </c>
       <c r="I26" t="n">
-        <v>3399</v>
+        <v>276</v>
       </c>
       <c r="J26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>83.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="M26" t="n">
-        <v>18129</v>
+        <v>19776</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -5868,7 +5278,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SO2103</t>
+          <t>SO2303</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5877,28 +5287,48 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11463</v>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+        <v>7897</v>
+      </c>
+      <c r="D27" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5080</v>
+      </c>
+      <c r="F27" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2679</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>92</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>46</v>
+      </c>
+      <c r="L27" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2817</v>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SO2203</t>
+          <t>SO2307</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5907,37 +5337,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>218656</v>
+        <v>1932</v>
       </c>
       <c r="D28" t="n">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
       <c r="E28" t="n">
-        <v>14577</v>
+        <v>81</v>
       </c>
       <c r="F28" t="n">
-        <v>86.7</v>
+        <v>76.5</v>
       </c>
       <c r="G28" t="n">
-        <v>189502</v>
+        <v>1477</v>
       </c>
       <c r="H28" t="n">
-        <v>5.2</v>
+        <v>17.6</v>
       </c>
       <c r="I28" t="n">
-        <v>11338</v>
+        <v>341</v>
       </c>
       <c r="J28" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="K28" t="n">
-        <v>3239</v>
+        <v>32</v>
       </c>
       <c r="L28" t="n">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="M28" t="n">
-        <v>204079</v>
+        <v>1851</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -5948,7 +5378,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SO2210</t>
+          <t>SO2401</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5957,37 +5387,37 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>222742</v>
+        <v>214369</v>
       </c>
       <c r="D29" t="n">
-        <v>3.8</v>
+        <v>15.5</v>
       </c>
       <c r="E29" t="n">
-        <v>8428</v>
+        <v>33322</v>
       </c>
       <c r="F29" t="n">
-        <v>90.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>201070</v>
+        <v>177715</v>
       </c>
       <c r="H29" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>13244</v>
+        <v>2221</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1111</v>
       </c>
       <c r="L29" t="n">
-        <v>96.2</v>
+        <v>84.5</v>
       </c>
       <c r="M29" t="n">
-        <v>214314</v>
+        <v>181047</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -5998,7 +5428,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SO2301</t>
+          <t>SO2402</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6007,37 +5437,37 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7265</v>
+        <v>1277</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>19.5</v>
       </c>
       <c r="E30" t="n">
-        <v>149</v>
+        <v>249</v>
       </c>
       <c r="F30" t="n">
-        <v>93.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="G30" t="n">
-        <v>6818</v>
+        <v>920</v>
       </c>
       <c r="H30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>97</v>
+      </c>
+      <c r="J30" t="n">
         <v>0.8</v>
       </c>
-      <c r="I30" t="n">
-        <v>60</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3.3</v>
-      </c>
       <c r="K30" t="n">
-        <v>238</v>
+        <v>11</v>
       </c>
       <c r="L30" t="n">
-        <v>98</v>
+        <v>80.5</v>
       </c>
       <c r="M30" t="n">
-        <v>7116</v>
+        <v>1028</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -6048,7 +5478,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SO2302</t>
+          <t>SO2403</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6057,37 +5487,37 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>22260</v>
+        <v>9741</v>
       </c>
       <c r="D31" t="n">
-        <v>11.2</v>
+        <v>1.9</v>
       </c>
       <c r="E31" t="n">
-        <v>2484</v>
+        <v>190</v>
       </c>
       <c r="F31" t="n">
-        <v>87.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="G31" t="n">
-        <v>19500</v>
+        <v>9400</v>
       </c>
       <c r="H31" t="n">
         <v>1.2</v>
       </c>
       <c r="I31" t="n">
-        <v>276</v>
+        <v>114</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L31" t="n">
-        <v>88.8</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>19776</v>
+        <v>9551</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -6098,7 +5528,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SO2303</t>
+          <t>SO2404</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6107,37 +5537,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7897</v>
+        <v>20291</v>
       </c>
       <c r="D32" t="n">
-        <v>64.3</v>
+        <v>24</v>
       </c>
       <c r="E32" t="n">
-        <v>5080</v>
+        <v>4863</v>
       </c>
       <c r="F32" t="n">
-        <v>33.9</v>
+        <v>74</v>
       </c>
       <c r="G32" t="n">
-        <v>2679</v>
+        <v>15009</v>
       </c>
       <c r="H32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I32" t="n">
+        <v>168</v>
+      </c>
+      <c r="J32" t="n">
         <v>1.2</v>
       </c>
-      <c r="I32" t="n">
-        <v>92</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.6</v>
-      </c>
       <c r="K32" t="n">
-        <v>46</v>
+        <v>252</v>
       </c>
       <c r="L32" t="n">
-        <v>35.7</v>
+        <v>76</v>
       </c>
       <c r="M32" t="n">
-        <v>2817</v>
+        <v>15428</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -6148,7 +5578,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SO2307</t>
+          <t>SO2501</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6157,37 +5587,37 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1932</v>
+        <v>21382</v>
       </c>
       <c r="D33" t="n">
-        <v>4.2</v>
+        <v>20.9</v>
       </c>
       <c r="E33" t="n">
-        <v>81</v>
+        <v>4468</v>
       </c>
       <c r="F33" t="n">
-        <v>76.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>1477</v>
+        <v>15957</v>
       </c>
       <c r="H33" t="n">
-        <v>17.6</v>
+        <v>1.9</v>
       </c>
       <c r="I33" t="n">
-        <v>341</v>
+        <v>399</v>
       </c>
       <c r="J33" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="K33" t="n">
-        <v>32</v>
+        <v>558</v>
       </c>
       <c r="L33" t="n">
-        <v>95.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>1851</v>
+        <v>16914</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -6198,7 +5628,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SO2401</t>
+          <t>SO2502</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6207,37 +5637,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>214369</v>
+        <v>2706</v>
       </c>
       <c r="D34" t="n">
-        <v>15.5</v>
+        <v>31.6</v>
       </c>
       <c r="E34" t="n">
-        <v>33322</v>
+        <v>856</v>
       </c>
       <c r="F34" t="n">
-        <v>82.90000000000001</v>
+        <v>53.2</v>
       </c>
       <c r="G34" t="n">
-        <v>177715</v>
+        <v>1439</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>13.9</v>
       </c>
       <c r="I34" t="n">
-        <v>2221</v>
+        <v>377</v>
       </c>
       <c r="J34" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="K34" t="n">
-        <v>1111</v>
+        <v>34</v>
       </c>
       <c r="L34" t="n">
-        <v>84.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>181047</v>
+        <v>1850</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -6248,7 +5678,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SO2402</t>
+          <t>SO2504</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6257,37 +5687,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1277</v>
+        <v>4578</v>
       </c>
       <c r="D35" t="n">
-        <v>19.5</v>
+        <v>18.3</v>
       </c>
       <c r="E35" t="n">
-        <v>249</v>
+        <v>838</v>
       </c>
       <c r="F35" t="n">
-        <v>72</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>920</v>
+        <v>3314</v>
       </c>
       <c r="H35" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>97</v>
+        <v>374</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K35" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="L35" t="n">
-        <v>80.5</v>
+        <v>81.7</v>
       </c>
       <c r="M35" t="n">
-        <v>1028</v>
+        <v>3740</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -6298,7 +5728,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SO2403</t>
+          <t>SO2601</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6307,37 +5737,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9741</v>
+        <v>3680</v>
       </c>
       <c r="D36" t="n">
-        <v>1.9</v>
+        <v>58.7</v>
       </c>
       <c r="E36" t="n">
-        <v>190</v>
+        <v>2158</v>
       </c>
       <c r="F36" t="n">
-        <v>96.5</v>
+        <v>32.7</v>
       </c>
       <c r="G36" t="n">
-        <v>9400</v>
+        <v>1203</v>
       </c>
       <c r="H36" t="n">
-        <v>1.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>114</v>
+        <v>307</v>
       </c>
       <c r="J36" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K36" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="L36" t="n">
-        <v>98.09999999999999</v>
+        <v>41.3</v>
       </c>
       <c r="M36" t="n">
-        <v>9551</v>
+        <v>1522</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -6348,7 +5778,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SO2404</t>
+          <t>SO2602</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6357,37 +5787,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>20291</v>
+        <v>34813</v>
       </c>
       <c r="D37" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E37" t="n">
-        <v>4863</v>
+        <v>5912</v>
       </c>
       <c r="F37" t="n">
-        <v>74</v>
+        <v>77.8</v>
       </c>
       <c r="G37" t="n">
-        <v>15009</v>
+        <v>27095</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="I37" t="n">
-        <v>168</v>
+        <v>1314</v>
       </c>
       <c r="J37" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="K37" t="n">
-        <v>252</v>
+        <v>493</v>
       </c>
       <c r="L37" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="M37" t="n">
-        <v>15428</v>
+        <v>28901</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -6398,7 +5828,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SO2501</t>
+          <t>SO2604</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6407,37 +5837,37 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>21382</v>
+        <v>5590</v>
       </c>
       <c r="D38" t="n">
-        <v>20.9</v>
+        <v>7.2</v>
       </c>
       <c r="E38" t="n">
-        <v>4468</v>
+        <v>404</v>
       </c>
       <c r="F38" t="n">
-        <v>74.59999999999999</v>
+        <v>90</v>
       </c>
       <c r="G38" t="n">
-        <v>15957</v>
+        <v>5029</v>
       </c>
       <c r="H38" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="I38" t="n">
-        <v>399</v>
+        <v>112</v>
       </c>
       <c r="J38" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="K38" t="n">
-        <v>558</v>
+        <v>45</v>
       </c>
       <c r="L38" t="n">
-        <v>79.09999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="M38" t="n">
-        <v>16914</v>
+        <v>5186</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -6448,7 +5878,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SO2502</t>
+          <t>SO2605</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6457,48 +5887,48 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2706</v>
+        <v>55127</v>
       </c>
       <c r="D39" t="n">
-        <v>31.6</v>
+        <v>63.6</v>
       </c>
       <c r="E39" t="n">
-        <v>856</v>
+        <v>35058</v>
       </c>
       <c r="F39" t="n">
-        <v>53.2</v>
+        <v>14.3</v>
       </c>
       <c r="G39" t="n">
-        <v>1439</v>
+        <v>7875</v>
       </c>
       <c r="H39" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="I39" t="n">
-        <v>377</v>
+        <v>7621</v>
       </c>
       <c r="J39" t="n">
-        <v>1.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>34</v>
+        <v>4573</v>
       </c>
       <c r="L39" t="n">
-        <v>68.40000000000001</v>
+        <v>36.4</v>
       </c>
       <c r="M39" t="n">
-        <v>1850</v>
+        <v>20069</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SO2504</t>
+          <t>SO2606</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6507,37 +5937,37 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4578</v>
+        <v>25164</v>
       </c>
       <c r="D40" t="n">
-        <v>18.3</v>
+        <v>36.8</v>
       </c>
       <c r="E40" t="n">
-        <v>838</v>
+        <v>9250</v>
       </c>
       <c r="F40" t="n">
-        <v>72.40000000000001</v>
+        <v>56.9</v>
       </c>
       <c r="G40" t="n">
-        <v>3314</v>
+        <v>14323</v>
       </c>
       <c r="H40" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="I40" t="n">
-        <v>374</v>
+        <v>1194</v>
       </c>
       <c r="J40" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="K40" t="n">
-        <v>52</v>
+        <v>398</v>
       </c>
       <c r="L40" t="n">
-        <v>81.7</v>
+        <v>63.2</v>
       </c>
       <c r="M40" t="n">
-        <v>3740</v>
+        <v>15914</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -6548,7 +5978,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SO2601</t>
+          <t>SO2801</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6557,37 +5987,37 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3680</v>
+        <v>80762</v>
       </c>
       <c r="D41" t="n">
-        <v>58.7</v>
+        <v>26.3</v>
       </c>
       <c r="E41" t="n">
-        <v>2158</v>
+        <v>21253</v>
       </c>
       <c r="F41" t="n">
-        <v>32.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>1203</v>
+        <v>57687</v>
       </c>
       <c r="H41" t="n">
-        <v>8.300000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="I41" t="n">
-        <v>307</v>
+        <v>1518</v>
       </c>
       <c r="J41" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K41" t="n">
-        <v>12</v>
+        <v>304</v>
       </c>
       <c r="L41" t="n">
-        <v>41.3</v>
+        <v>73.7</v>
       </c>
       <c r="M41" t="n">
-        <v>1522</v>
+        <v>59509</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -6598,7 +6028,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SO2602</t>
+          <t>SO2802</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6607,431 +6037,41 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>34813</v>
+        <v>26533</v>
       </c>
       <c r="D42" t="n">
-        <v>17</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>5912</v>
+        <v>2478</v>
       </c>
       <c r="F42" t="n">
-        <v>77.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>27095</v>
+        <v>21990</v>
       </c>
       <c r="H42" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="I42" t="n">
-        <v>1314</v>
+        <v>2065</v>
       </c>
       <c r="J42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>493</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>83</v>
+        <v>90.7</v>
       </c>
       <c r="M42" t="n">
-        <v>28901</v>
+        <v>24055</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>SO2603</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>idp</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>359</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>SO2604</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>idp</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>5590</v>
-      </c>
-      <c r="D44" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E44" t="n">
-        <v>404</v>
-      </c>
-      <c r="F44" t="n">
-        <v>90</v>
-      </c>
-      <c r="G44" t="n">
-        <v>5029</v>
-      </c>
-      <c r="H44" t="n">
-        <v>2</v>
-      </c>
-      <c r="I44" t="n">
-        <v>112</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K44" t="n">
-        <v>45</v>
-      </c>
-      <c r="L44" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="M44" t="n">
-        <v>5186</v>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>SO2605</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>idp</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>55127</v>
-      </c>
-      <c r="D45" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="E45" t="n">
-        <v>35058</v>
-      </c>
-      <c r="F45" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G45" t="n">
-        <v>7875</v>
-      </c>
-      <c r="H45" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="I45" t="n">
-        <v>7621</v>
-      </c>
-      <c r="J45" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K45" t="n">
-        <v>4573</v>
-      </c>
-      <c r="L45" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="M45" t="n">
-        <v>20069</v>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>SO2606</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>idp</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>25164</v>
-      </c>
-      <c r="D46" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="E46" t="n">
-        <v>9250</v>
-      </c>
-      <c r="F46" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="G46" t="n">
-        <v>14323</v>
-      </c>
-      <c r="H46" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1194</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K46" t="n">
-        <v>398</v>
-      </c>
-      <c r="L46" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="M46" t="n">
-        <v>15914</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>SO2701</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>idp</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>SO2702</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>idp</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>SO2801</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>idp</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>80762</v>
-      </c>
-      <c r="D49" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E49" t="n">
-        <v>21253</v>
-      </c>
-      <c r="F49" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="G49" t="n">
-        <v>57687</v>
-      </c>
-      <c r="H49" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I49" t="n">
-        <v>1518</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K49" t="n">
-        <v>304</v>
-      </c>
-      <c r="L49" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="M49" t="n">
-        <v>59509</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>SO2802</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>idp</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>26533</v>
-      </c>
-      <c r="D50" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="E50" t="n">
-        <v>2478</v>
-      </c>
-      <c r="F50" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="G50" t="n">
-        <v>21990</v>
-      </c>
-      <c r="H50" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2065</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="M50" t="n">
-        <v>24055</v>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>SO2804</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>idp</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
